--- a/examples/mosconi/decaf_2024.xlsx
+++ b/examples/mosconi/decaf_2024.xlsx
@@ -647,27 +647,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -688,75 +689,80 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
+          <t>Azienda</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Paese</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Acquisto</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Vendita</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Val. iniz. orig.</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Val. fin. orig.</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Cambio iniz.</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Cambio fin.</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Val. iniz. EUR</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>Val. fin. EUR</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>Giorni</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>Quota %</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>IVAFE</t>
         </is>
@@ -778,53 +784,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>MAKEOO SBATTE LA PORTA SPA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>MKEO (2023-03-17)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>100</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2023-03-17</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" s="4" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>1200</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.105</v>
-      </c>
       <c r="M2" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="N2" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="O2" s="4" t="n">
         <v>904.98</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="P2" s="4" t="n">
         <v>1155.07</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>366</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>100</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="S2" s="4" t="n">
         <v>2.31</v>
       </c>
     </row>
@@ -844,53 +855,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>SBATTE LA PORTA PRODUCTIONS INC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>SBTP (2023-04-12)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>200</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2023-04-12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" s="4" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" s="4" t="n">
         <v>16000</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>22400</v>
       </c>
-      <c r="L3" t="n">
-        <v>1.105</v>
-      </c>
       <c r="M3" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="N3" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="O3" s="4" t="n">
         <v>14479.64</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="P3" s="4" t="n">
         <v>21561.27</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>366</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>100</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>43.12</v>
       </c>
     </row>
@@ -910,57 +926,62 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>PRCD BROADCASTING INC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>PRCD (2023-06-22)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>30</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2023-06-22</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>360</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>420</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.105</v>
-      </c>
       <c r="M4" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="N4" t="n">
         <v>1.1139</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="O4" s="4" t="n">
         <v>325.79</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="P4" s="4" t="n">
         <v>377.05</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>261</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>100</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="S4" s="4" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -980,53 +1001,58 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>PRCD BROADCASTING INC</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>PRCD (2023-06-22)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>70</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2023-06-22</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" s="4" t="n">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" s="4" t="n">
         <v>840</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="L5" s="4" t="n">
         <v>980</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.105</v>
-      </c>
       <c r="M5" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="N5" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="O5" s="4" t="n">
         <v>760.1799999999999</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="P5" s="4" t="n">
         <v>943.3099999999999</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>366</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>100</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="S5" s="4" t="n">
         <v>1.89</v>
       </c>
     </row>
@@ -1046,53 +1072,58 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>PRCMDN ASSET MANAGEMENT SPA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>PRCMDN (2023-09-07)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>300</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>2023-09-07</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" s="4" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="L6" s="4" t="n">
         <v>1650</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="4" t="n">
         <v>1500</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="P6" s="4" t="n">
         <v>1650</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>366</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>100</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -1112,57 +1143,62 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>PRCD BROADCASTING INC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>PRCD (2024-03-12)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>50</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2024-03-12</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>750</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="L7" s="4" t="n">
         <v>700</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1.0916</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1.1139</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="O7" s="4" t="n">
         <v>687.0599999999999</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="P7" s="4" t="n">
         <v>628.42</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>190</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>100</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="S7" s="4" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -1178,53 +1214,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>SBATTE LA PORTA PRODUCTIONS INC CLASS A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>SBTP (2024-03-17)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>15</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2024-03-17</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>1425</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="L8" s="4" t="n">
         <v>1725</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1.0892</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1.0897</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="O8" s="4" t="n">
         <v>1308.3</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="P8" s="4" t="n">
         <v>1583</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>214</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>100</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>1.85</v>
       </c>
     </row>
@@ -1240,53 +1281,58 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>SBATTE LA PORTA PRODUCTIONS INC CLASS A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>SBTP (2024-06-17)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>5</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2024-06-17</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2024-10-16</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="L9" s="4" t="n">
         <v>575</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1.0712</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>1.0897</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>466.77</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="P9" s="4" t="n">
         <v>527.67</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>122</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>100</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -1302,49 +1348,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>SBATTE LA PORTA PRODUCTIONS INC CLASS A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>SBTP (2024-06-17)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>10</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>2024-06-17</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" s="4" t="n">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="L10" s="4" t="n">
         <v>1120</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1.0712</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="O10" s="4" t="n">
         <v>933.53</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="P10" s="4" t="n">
         <v>1078.06</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>198</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>100</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>1.17</v>
       </c>
     </row>
@@ -1360,49 +1411,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>SBATTE LA PORTA PRODUCTIONS INC CLASS A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>SBTP (2024-09-17)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>15</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2024-09-17</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" s="4" t="n">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" s="4" t="n">
         <v>1575</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="L11" s="4" t="n">
         <v>1680</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>1.1139</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="O11" s="4" t="n">
         <v>1413.95</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="P11" s="4" t="n">
         <v>1617.1</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>106</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>100</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>0.9399999999999999</v>
       </c>
     </row>
@@ -1418,54 +1474,59 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>SBATTE LA PORTA PRODUCTIONS INC CLASS A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SBTP (2024-12-17)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>15</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2024-12-17</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" s="4" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" s="4" t="n">
         <v>1650</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="L12" s="4" t="n">
         <v>1680</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1.0497</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1.0389</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="O12" s="4" t="n">
         <v>1571.88</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="P12" s="4" t="n">
         <v>1617.1</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>15</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>100</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>0.13</v>
       </c>
     </row>
     <row r="13">
-      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1476,12 +1537,12 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>TOTALE</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1489,7 +1550,8 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" s="4" t="n">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" s="4" t="n">
         <v>56.25</v>
       </c>
     </row>
@@ -1504,21 +1566,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1534,50 +1597,55 @@
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
+          <t>Azienda</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
           <t>Data acquisto</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Data vendita</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Corrispettivo EUR</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Costo EUR</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>+/- EUR</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Cambio BCE</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>Forex</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>P/L broker</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>P/L broker EUR</t>
         </is>
@@ -1596,38 +1664,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>PRCD BROADCASTING INC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>80</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="G2" s="4" t="n">
         <v>1005.48</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>861.84</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>143.64</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>1.1139</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="L2" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="M2" s="4" t="n">
         <v>143.64</v>
       </c>
     </row>
@@ -1644,38 +1717,43 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>SBTP (acquired 2024-03-15)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2024-03-15</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>15</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>1583</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>1307.7</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>275.31</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1.0897</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="L3" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="M3" s="4" t="n">
         <v>275.31</v>
       </c>
     </row>
@@ -1692,43 +1770,48 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>SBTP (acquired 2024-06-15)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2024-06-15</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>527.67</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>458.84</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>68.83</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1.0897</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="L4" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>68.83</v>
       </c>
     </row>
     <row r="5">
-      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1737,12 +1820,13 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>NETTO</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>487.78</v>
       </c>
     </row>

--- a/examples/mosconi/decaf_2024.xlsx
+++ b/examples/mosconi/decaf_2024.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>56.25</v>
+        <v>56.23</v>
       </c>
     </row>
     <row r="14">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>487.78</v>
+        <v>461.87</v>
       </c>
     </row>
     <row r="15">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="K4" s="4" t="n">
-        <v>360</v>
+        <v>960</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>420</v>
+        <v>1120</v>
       </c>
       <c r="M4" t="n">
         <v>1.105</v>
@@ -970,10 +970,10 @@
         <v>1.1139</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>325.79</v>
+        <v>868.78</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>377.05</v>
+        <v>1005.48</v>
       </c>
       <c r="Q4" t="n">
         <v>261</v>
@@ -982,7 +982,7 @@
         <v>100</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.54</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="5">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" s="4" t="n">
-        <v>840</v>
+        <v>240</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>980</v>
+        <v>280</v>
       </c>
       <c r="M5" t="n">
         <v>1.105</v>
@@ -1041,10 +1041,10 @@
         <v>1.0389</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>760.1799999999999</v>
+        <v>217.19</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>943.3099999999999</v>
+        <v>269.52</v>
       </c>
       <c r="Q5" t="n">
         <v>366</v>
@@ -1053,7 +1053,7 @@
         <v>100</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>1.89</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="6">
@@ -1169,11 +1169,7 @@
           <t>2024-03-12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" s="4" t="n">
         <v>750</v>
       </c>
@@ -1184,22 +1180,22 @@
         <v>1.0916</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1139</v>
+        <v>1.0389</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>687.0599999999999</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>628.42</v>
+        <v>673.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>190</v>
+        <v>295</v>
       </c>
       <c r="R7" t="n">
         <v>100</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.65</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="8">
@@ -1552,7 +1548,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" s="4" t="n">
-        <v>56.25</v>
+        <v>56.23</v>
       </c>
     </row>
   </sheetData>
@@ -1669,12 +1665,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024-09-15</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1684,10 +1680,10 @@
         <v>1005.48</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>861.84</v>
+        <v>878.08</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>143.64</v>
+        <v>127.4</v>
       </c>
       <c r="J2" t="n">
         <v>1.1139</v>
@@ -1727,7 +1723,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1737,10 +1733,10 @@
         <v>1583</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1307.7</v>
+        <v>1308.3</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>275.31</v>
+        <v>274.7</v>
       </c>
       <c r="J3" t="n">
         <v>1.0897</v>
@@ -1780,7 +1776,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1790,10 +1786,10 @@
         <v>527.67</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>458.84</v>
+        <v>467.9</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>68.83</v>
+        <v>59.77</v>
       </c>
       <c r="J4" t="n">
         <v>1.0897</v>
@@ -1827,7 +1823,7 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>487.78</v>
+        <v>461.87</v>
       </c>
     </row>
   </sheetData>

--- a/examples/mosconi/decaf_2024.xlsx
+++ b/examples/mosconi/decaf_2024.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,10 @@
     <font>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,12 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -443,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -636,7 +641,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Controllo coerenza RSU (art. 9 c. 4 TUIR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vest events nell'anno</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Reddito RSU tassato (EUR)</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>5702.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Cross-check: deve essere sottoinsieme del punto 1 CU "Redditi di lavoro dipendente". Differenza = stipendio + bonus.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A26:D26"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -672,97 +717,97 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Cod.</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Simbolo</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Paese</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Acquisto</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Vendita</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Val. iniz. orig.</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Val. fin. orig.</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Cambio iniz.</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Cambio fin.</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Val. iniz. EUR</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Val. fin. EUR</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Giorni</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>Quota %</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>IVAFE</t>
         </is>
@@ -1522,7 +1567,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="S13" s="6" t="n"/>
+      <c r="S13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1581,67 +1626,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Simbolo</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>ISIN</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Data acquisto</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Data vendita</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Quantita</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Corrispettivo EUR</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Costo EUR</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>+/- EUR</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Cambio BCE</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Forex</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>P/L broker</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>P/L broker EUR</t>
         </is>
@@ -1807,7 +1852,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="I5" s="6" t="n"/>
+      <c r="I5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1850,37 +1895,37 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Descrizione</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Valuta</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Lordo</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Lordo EUR</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Ritenuta</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Ritenuta EUR</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Netto EUR</t>
         </is>
@@ -1941,9 +1986,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="D4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -2020,32 +2065,32 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Saldo USD</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Equiv. EUR</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Giorno lavorativo</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Sopra soglia</t>
         </is>
